--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E520"/>
+  <dimension ref="A1:E523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11350,6 +11350,69 @@
         <v>358.94</v>
       </c>
       <c r="E520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="C521" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="D521" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>343.05</v>
+      </c>
+      <c r="C522" t="n">
+        <v>347.67</v>
+      </c>
+      <c r="D522" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>343.3</v>
+      </c>
+      <c r="C523" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="D523" t="n">
+        <v>358.88</v>
+      </c>
+      <c r="E523" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11366,7 +11429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B688"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18249,6 +18312,36 @@
       </c>
       <c r="B688" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -18417,28 +18510,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1309637118293365</v>
+        <v>-0.1356008235046481</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06645755791816921</v>
+        <v>0.07122102581239353</v>
       </c>
       <c r="M2" t="n">
-        <v>2.743983901657399</v>
+        <v>2.750081940990956</v>
       </c>
       <c r="N2" t="n">
-        <v>11.83401445552314</v>
+        <v>11.85328674435957</v>
       </c>
       <c r="O2" t="n">
-        <v>3.440060240100911</v>
+        <v>3.442860256292661</v>
       </c>
       <c r="P2" t="n">
-        <v>350.497480915325</v>
+        <v>350.552394237504</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18495,28 +18588,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1201949030363525</v>
+        <v>-0.1223485485117867</v>
       </c>
       <c r="J3" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="K3" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07567539204811946</v>
+        <v>0.07891802263489744</v>
       </c>
       <c r="M3" t="n">
-        <v>2.36660297212082</v>
+        <v>2.362499363120374</v>
       </c>
       <c r="N3" t="n">
-        <v>8.667271363731089</v>
+        <v>8.636339739371492</v>
       </c>
       <c r="O3" t="n">
-        <v>2.944022989674349</v>
+        <v>2.938765002406877</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5396278912174</v>
+        <v>352.5651322151208</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18573,28 +18666,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04795390047925699</v>
+        <v>0.04584729264737154</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01037212878953453</v>
+        <v>0.009587902307805596</v>
       </c>
       <c r="M4" t="n">
-        <v>2.622547408914383</v>
+        <v>2.617144590085627</v>
       </c>
       <c r="N4" t="n">
-        <v>10.79270117692525</v>
+        <v>10.7487577778403</v>
       </c>
       <c r="O4" t="n">
-        <v>3.285224676780151</v>
+        <v>3.278529819574667</v>
       </c>
       <c r="P4" t="n">
-        <v>359.196824258001</v>
+        <v>359.2217620569696</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18632,7 +18725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E520"/>
+  <dimension ref="A1:E523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32671,6 +32764,87 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-45.369100495349244,170.86457627926325</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-45.36970849274595,170.8646423085477</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-45.3702467164998,170.86510578196052</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-45.3691005170283,170.86457934289058</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-45.369708000019834,170.86464620374733</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-45.370245696876445,170.86510960239332</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-45.36910053961058,170.86458253416905</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-45.369708381485225,170.86464318810891</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-45.370245346380884,170.86511091566706</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E523"/>
+  <dimension ref="A1:E525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11413,6 +11413,48 @@
         <v>358.88</v>
       </c>
       <c r="E523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="C524" t="n">
+        <v>347.15</v>
+      </c>
+      <c r="D524" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>344.01</v>
+      </c>
+      <c r="C525" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="D525" t="n">
+        <v>359.15</v>
+      </c>
+      <c r="E525" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11429,7 +11471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18342,6 +18384,26 @@
       </c>
       <c r="B691" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -18510,28 +18572,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1356008235046481</v>
+        <v>-0.1380674826296403</v>
       </c>
       <c r="J2" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07122102581239353</v>
+        <v>0.07397926138071753</v>
       </c>
       <c r="M2" t="n">
-        <v>2.750081940990956</v>
+        <v>2.751191136755539</v>
       </c>
       <c r="N2" t="n">
-        <v>11.85328674435957</v>
+        <v>11.84551611152953</v>
       </c>
       <c r="O2" t="n">
-        <v>3.442860256292661</v>
+        <v>3.441731557156882</v>
       </c>
       <c r="P2" t="n">
-        <v>350.552394237504</v>
+        <v>350.5817154217994</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18588,28 +18650,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1223485485117867</v>
+        <v>-0.1239787780213501</v>
       </c>
       <c r="J3" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07891802263489744</v>
+        <v>0.08132569233076503</v>
       </c>
       <c r="M3" t="n">
-        <v>2.362499363120374</v>
+        <v>2.360578437174492</v>
       </c>
       <c r="N3" t="n">
-        <v>8.636339739371492</v>
+        <v>8.619636615162948</v>
       </c>
       <c r="O3" t="n">
-        <v>2.938765002406877</v>
+        <v>2.93592176584509</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5651322151208</v>
+        <v>352.5845118161276</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18666,28 +18728,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04584729264737154</v>
+        <v>0.04468188120823658</v>
       </c>
       <c r="J4" t="n">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009587902307805596</v>
+        <v>0.009177088811208711</v>
       </c>
       <c r="M4" t="n">
-        <v>2.617144590085627</v>
+        <v>2.612430144203334</v>
       </c>
       <c r="N4" t="n">
-        <v>10.7487577778403</v>
+        <v>10.71610358718046</v>
       </c>
       <c r="O4" t="n">
-        <v>3.278529819574667</v>
+        <v>3.27354602643379</v>
       </c>
       <c r="P4" t="n">
-        <v>359.2217620569696</v>
+        <v>359.2356108131065</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18725,7 +18787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E523"/>
+  <dimension ref="A1:E525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32845,6 +32907,60 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-45.369100557676326,170.8645850871918</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-45.369708826528075,170.86463966986406</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-45.37024563314999,170.86510984117035</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-45.36910060374373,170.8645915973999</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-45.369708699372985,170.86464067507688</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-45.370244486073545,170.86511413915707</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0486/nzd0486.xlsx
+++ b/data/nzd0486/nzd0486.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11455,6 +11455,48 @@
         <v>359.15</v>
       </c>
       <c r="E525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="C526" t="n">
+        <v>347.13</v>
+      </c>
+      <c r="D526" t="n">
+        <v>358.97</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="C527" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="D527" t="n">
+        <v>361.77</v>
+      </c>
+      <c r="E527" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11471,7 +11513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18404,6 +18446,26 @@
       </c>
       <c r="B693" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -18572,28 +18634,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1380674826296403</v>
+        <v>-0.1395575567398347</v>
       </c>
       <c r="J2" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K2" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07397926138071753</v>
+        <v>0.07592881020193498</v>
       </c>
       <c r="M2" t="n">
-        <v>2.751191136755539</v>
+        <v>2.747671629523762</v>
       </c>
       <c r="N2" t="n">
-        <v>11.84551611152953</v>
+        <v>11.81735125961305</v>
       </c>
       <c r="O2" t="n">
-        <v>3.441731557156882</v>
+        <v>3.437637453195588</v>
       </c>
       <c r="P2" t="n">
-        <v>350.5817154217994</v>
+        <v>350.5994719922336</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18650,28 +18712,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1239787780213501</v>
+        <v>-0.1250826561388001</v>
       </c>
       <c r="J3" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08132569233076503</v>
+        <v>0.08319198516084902</v>
       </c>
       <c r="M3" t="n">
-        <v>2.360578437174492</v>
+        <v>2.356383509683151</v>
       </c>
       <c r="N3" t="n">
-        <v>8.619636615162948</v>
+        <v>8.596183889487541</v>
       </c>
       <c r="O3" t="n">
-        <v>2.93592176584509</v>
+        <v>2.931924946087048</v>
       </c>
       <c r="P3" t="n">
-        <v>352.5845118161276</v>
+        <v>352.5976661153278</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18728,28 +18790,28 @@
         <v>0.0883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04468188120823658</v>
+        <v>0.04462928144453394</v>
       </c>
       <c r="J4" t="n">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009177088811208711</v>
+        <v>0.009222836312005156</v>
       </c>
       <c r="M4" t="n">
-        <v>2.612430144203334</v>
+        <v>2.607780822546973</v>
       </c>
       <c r="N4" t="n">
-        <v>10.71610358718046</v>
+        <v>10.68272946293799</v>
       </c>
       <c r="O4" t="n">
-        <v>3.27354602643379</v>
+        <v>3.26844450204344</v>
       </c>
       <c r="P4" t="n">
-        <v>359.2356108131065</v>
+        <v>359.236220778602</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18787,7 +18849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32961,6 +33023,60 @@
         </is>
       </c>
     </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-45.369100605550294,170.8645918527022</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-45.369708858316855,170.86463941856084</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-45.370245059611776,170.86511199016374</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-45.36910076994464,170.86461508520975</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-45.369706680784724,170.86465663282988</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-45.37023613790112,170.86514541894428</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
